--- a/重点商品CA別進捗_2026年9月.xlsx
+++ b/重点商品CA別進捗_2026年9月.xlsx
@@ -16,13 +16,13 @@
     <sheet name="クエスト5・U-Car石川" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'石川'!$A$1:$E$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'亀本'!$A$1:$E$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'神山'!$A$1:$E$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'森'!$A$1:$E$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'北檜山'!$A$1:$E$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">'江差'!$A$1:$E$5</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">'クエスト5・U-Car石川'!$A$1:$E$5</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'石川'!$A$1:$E$8</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'亀本'!$A$1:$E$8</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'神山'!$A$1:$E$8</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'森'!$A$1:$E$8</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'北檜山'!$A$1:$E$8</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'江差'!$A$1:$E$8</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'クエスト5・U-Car石川'!$A$1:$E$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -213,7 +213,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="13"/>
+              <ptCount val="9"/>
               <pt idx="0">
                 <v>加藤　英基</v>
               </pt>
@@ -239,25 +239,13 @@
                 <v>岩坪　公夫</v>
               </pt>
               <pt idx="8">
-                <v>落合　典彦</v>
-              </pt>
-              <pt idx="9">
-                <v>鈴木　聡</v>
-              </pt>
-              <pt idx="10">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="11">
-                <v>前野　正樹</v>
-              </pt>
-              <pt idx="12">
-                <v>石澤　直道</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="13"/>
+              <ptCount val="9"/>
               <pt idx="0">
                 <v>0</v>
               </pt>
@@ -283,18 +271,6 @@
                 <v>0</v>
               </pt>
               <pt idx="8">
-                <v>0</v>
-              </pt>
-              <pt idx="9">
-                <v>0</v>
-              </pt>
-              <pt idx="10">
-                <v>0</v>
-              </pt>
-              <pt idx="11">
-                <v>0</v>
-              </pt>
-              <pt idx="12">
                 <v>0</v>
               </pt>
             </numLit>
@@ -359,6 +335,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -409,7 +393,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="13"/>
+              <ptCount val="9"/>
               <pt idx="0">
                 <v>加藤　英基</v>
               </pt>
@@ -435,25 +419,13 @@
                 <v>岩坪　公夫</v>
               </pt>
               <pt idx="8">
-                <v>落合　典彦</v>
-              </pt>
-              <pt idx="9">
-                <v>鈴木　聡</v>
-              </pt>
-              <pt idx="10">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="11">
-                <v>前野　正樹</v>
-              </pt>
-              <pt idx="12">
-                <v>石澤　直道</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="13"/>
+              <ptCount val="9"/>
               <pt idx="0">
                 <v>0</v>
               </pt>
@@ -461,7 +433,7 @@
                 <v>0</v>
               </pt>
               <pt idx="2">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="3">
                 <v>0</v>
@@ -479,18 +451,6 @@
                 <v>0</v>
               </pt>
               <pt idx="8">
-                <v>0</v>
-              </pt>
-              <pt idx="9">
-                <v>0</v>
-              </pt>
-              <pt idx="10">
-                <v>0</v>
-              </pt>
-              <pt idx="11">
-                <v>0</v>
-              </pt>
-              <pt idx="12">
                 <v>0</v>
               </pt>
             </numLit>
@@ -555,6 +515,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -605,7 +573,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="6"/>
+              <ptCount val="7"/>
               <pt idx="0">
                 <v>大島　貞男</v>
               </pt>
@@ -623,17 +591,20 @@
               </pt>
               <pt idx="5">
                 <v>田中　智久</v>
+              </pt>
+              <pt idx="6">
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="6"/>
+              <ptCount val="7"/>
               <pt idx="0">
                 <v>0</v>
               </pt>
               <pt idx="1">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="2">
                 <v>0</v>
@@ -645,6 +616,9 @@
                 <v>1</v>
               </pt>
               <pt idx="5">
+                <v>0</v>
+              </pt>
+              <pt idx="6">
                 <v>0</v>
               </pt>
             </numLit>
@@ -709,6 +683,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -759,7 +741,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="6"/>
+              <ptCount val="7"/>
               <pt idx="0">
                 <v>大島　貞男</v>
               </pt>
@@ -777,12 +759,15 @@
               </pt>
               <pt idx="5">
                 <v>田中　智久</v>
+              </pt>
+              <pt idx="6">
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="6"/>
+              <ptCount val="7"/>
               <pt idx="0">
                 <v>0</v>
               </pt>
@@ -799,6 +784,9 @@
                 <v>0</v>
               </pt>
               <pt idx="5">
+                <v>0</v>
+              </pt>
+              <pt idx="6">
                 <v>0</v>
               </pt>
             </numLit>
@@ -863,6 +851,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -913,7 +909,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="6"/>
+              <ptCount val="7"/>
               <pt idx="0">
                 <v>大島　貞男</v>
               </pt>
@@ -931,12 +927,15 @@
               </pt>
               <pt idx="5">
                 <v>田中　智久</v>
+              </pt>
+              <pt idx="6">
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="6"/>
+              <ptCount val="7"/>
               <pt idx="0">
                 <v>0</v>
               </pt>
@@ -954,6 +953,9 @@
               </pt>
               <pt idx="5">
                 <v>1</v>
+              </pt>
+              <pt idx="6">
+                <v>0</v>
               </pt>
             </numLit>
           </val>
@@ -1017,6 +1019,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -1067,7 +1077,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="6"/>
+              <ptCount val="7"/>
               <pt idx="0">
                 <v>大島　貞男</v>
               </pt>
@@ -1085,12 +1095,15 @@
               </pt>
               <pt idx="5">
                 <v>田中　智久</v>
+              </pt>
+              <pt idx="6">
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="6"/>
+              <ptCount val="7"/>
               <pt idx="0">
                 <v>0</v>
               </pt>
@@ -1101,12 +1114,15 @@
                 <v>0</v>
               </pt>
               <pt idx="3">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="4">
                 <v>1</v>
               </pt>
               <pt idx="5">
+                <v>0</v>
+              </pt>
+              <pt idx="6">
                 <v>0</v>
               </pt>
             </numLit>
@@ -1171,6 +1187,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -1221,7 +1245,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="6"/>
+              <ptCount val="7"/>
               <pt idx="0">
                 <v>大島　貞男</v>
               </pt>
@@ -1239,12 +1263,15 @@
               </pt>
               <pt idx="5">
                 <v>田中　智久</v>
+              </pt>
+              <pt idx="6">
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="6"/>
+              <ptCount val="7"/>
               <pt idx="0">
                 <v>0</v>
               </pt>
@@ -1261,6 +1288,9 @@
                 <v>0</v>
               </pt>
               <pt idx="5">
+                <v>0</v>
+              </pt>
+              <pt idx="6">
                 <v>0</v>
               </pt>
             </numLit>
@@ -1325,6 +1355,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -1375,7 +1413,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="6"/>
+              <ptCount val="7"/>
               <pt idx="0">
                 <v>大島　貞男</v>
               </pt>
@@ -1393,12 +1431,15 @@
               </pt>
               <pt idx="5">
                 <v>田中　智久</v>
+              </pt>
+              <pt idx="6">
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="6"/>
+              <ptCount val="7"/>
               <pt idx="0">
                 <v>0</v>
               </pt>
@@ -1416,6 +1457,9 @@
               </pt>
               <pt idx="5">
                 <v>1</v>
+              </pt>
+              <pt idx="6">
+                <v>0</v>
               </pt>
             </numLit>
           </val>
@@ -1461,7 +1505,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="7"/>
+          <max val="6"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -1479,6 +1523,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -1529,7 +1581,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="6"/>
+              <ptCount val="7"/>
               <pt idx="0">
                 <v>大島　貞男</v>
               </pt>
@@ -1547,12 +1599,15 @@
               </pt>
               <pt idx="5">
                 <v>田中　智久</v>
+              </pt>
+              <pt idx="6">
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="6"/>
+              <ptCount val="7"/>
               <pt idx="0">
                 <v>0</v>
               </pt>
@@ -1569,6 +1624,9 @@
                 <v>0</v>
               </pt>
               <pt idx="5">
+                <v>0</v>
+              </pt>
+              <pt idx="6">
                 <v>0</v>
               </pt>
             </numLit>
@@ -1633,6 +1691,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -1683,7 +1749,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="6"/>
+              <ptCount val="7"/>
               <pt idx="0">
                 <v>大島　貞男</v>
               </pt>
@@ -1701,17 +1767,20 @@
               </pt>
               <pt idx="5">
                 <v>田中　智久</v>
+              </pt>
+              <pt idx="6">
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="6"/>
+              <ptCount val="7"/>
               <pt idx="0">
                 <v>0</v>
               </pt>
               <pt idx="1">
-                <v>1</v>
+                <v>3</v>
               </pt>
               <pt idx="2">
                 <v>4</v>
@@ -1724,6 +1793,9 @@
               </pt>
               <pt idx="5">
                 <v>2</v>
+              </pt>
+              <pt idx="6">
+                <v>0</v>
               </pt>
             </numLit>
           </val>
@@ -1787,6 +1859,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -1837,7 +1917,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="6"/>
+              <ptCount val="7"/>
               <pt idx="0">
                 <v>大島　貞男</v>
               </pt>
@@ -1855,12 +1935,15 @@
               </pt>
               <pt idx="5">
                 <v>田中　智久</v>
+              </pt>
+              <pt idx="6">
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="6"/>
+              <ptCount val="7"/>
               <pt idx="0">
                 <v>0</v>
               </pt>
@@ -1877,6 +1960,9 @@
                 <v>0</v>
               </pt>
               <pt idx="5">
+                <v>0</v>
+              </pt>
+              <pt idx="6">
                 <v>0</v>
               </pt>
             </numLit>
@@ -1941,6 +2027,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -1991,7 +2085,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="13"/>
+              <ptCount val="9"/>
               <pt idx="0">
                 <v>加藤　英基</v>
               </pt>
@@ -2017,25 +2111,13 @@
                 <v>岩坪　公夫</v>
               </pt>
               <pt idx="8">
-                <v>落合　典彦</v>
-              </pt>
-              <pt idx="9">
-                <v>鈴木　聡</v>
-              </pt>
-              <pt idx="10">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="11">
-                <v>前野　正樹</v>
-              </pt>
-              <pt idx="12">
-                <v>石澤　直道</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="13"/>
+              <ptCount val="9"/>
               <pt idx="0">
                 <v>0</v>
               </pt>
@@ -2061,18 +2143,6 @@
                 <v>0</v>
               </pt>
               <pt idx="8">
-                <v>0</v>
-              </pt>
-              <pt idx="9">
-                <v>0</v>
-              </pt>
-              <pt idx="10">
-                <v>0</v>
-              </pt>
-              <pt idx="11">
-                <v>0</v>
-              </pt>
-              <pt idx="12">
                 <v>0</v>
               </pt>
             </numLit>
@@ -2137,6 +2207,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -2187,7 +2265,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="6"/>
+              <ptCount val="7"/>
               <pt idx="0">
                 <v>大島　貞男</v>
               </pt>
@@ -2205,12 +2283,15 @@
               </pt>
               <pt idx="5">
                 <v>田中　智久</v>
+              </pt>
+              <pt idx="6">
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="6"/>
+              <ptCount val="7"/>
               <pt idx="0">
                 <v>0</v>
               </pt>
@@ -2227,6 +2308,9 @@
                 <v>0</v>
               </pt>
               <pt idx="5">
+                <v>0</v>
+              </pt>
+              <pt idx="6">
                 <v>0</v>
               </pt>
             </numLit>
@@ -2291,6 +2375,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -2358,7 +2450,7 @@
                 <v>中原　義美</v>
               </pt>
               <pt idx="5">
-                <v>(担当CA不明)</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
@@ -2366,13 +2458,13 @@
             <numLit>
               <ptCount val="6"/>
               <pt idx="0">
-                <v>3</v>
+                <v>4</v>
               </pt>
               <pt idx="1">
                 <v>1</v>
               </pt>
               <pt idx="2">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="3">
                 <v>0</v>
@@ -2427,7 +2519,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="3"/>
+          <max val="4"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -2445,6 +2537,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -2512,7 +2612,7 @@
                 <v>中原　義美</v>
               </pt>
               <pt idx="5">
-                <v>(担当CA不明)</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
@@ -2520,7 +2620,7 @@
             <numLit>
               <ptCount val="6"/>
               <pt idx="0">
-                <v>2</v>
+                <v>3</v>
               </pt>
               <pt idx="1">
                 <v>1</v>
@@ -2599,6 +2699,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -2666,7 +2774,7 @@
                 <v>中原　義美</v>
               </pt>
               <pt idx="5">
-                <v>(担当CA不明)</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
@@ -2753,6 +2861,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -2820,7 +2936,7 @@
                 <v>中原　義美</v>
               </pt>
               <pt idx="5">
-                <v>(担当CA不明)</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
@@ -2828,7 +2944,7 @@
             <numLit>
               <ptCount val="6"/>
               <pt idx="0">
-                <v>2</v>
+                <v>3</v>
               </pt>
               <pt idx="1">
                 <v>1</v>
@@ -2907,6 +3023,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -2974,7 +3098,7 @@
                 <v>中原　義美</v>
               </pt>
               <pt idx="5">
-                <v>(担当CA不明)</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
@@ -2982,7 +3106,7 @@
             <numLit>
               <ptCount val="6"/>
               <pt idx="0">
-                <v>1</v>
+                <v>2</v>
               </pt>
               <pt idx="1">
                 <v>1</v>
@@ -3061,6 +3185,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -3128,7 +3260,7 @@
                 <v>中原　義美</v>
               </pt>
               <pt idx="5">
-                <v>(担当CA不明)</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
@@ -3136,7 +3268,7 @@
             <numLit>
               <ptCount val="6"/>
               <pt idx="0">
-                <v>3</v>
+                <v>4</v>
               </pt>
               <pt idx="1">
                 <v>1</v>
@@ -3197,7 +3329,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="7"/>
+          <max val="6"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -3215,6 +3347,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -3282,7 +3422,7 @@
                 <v>中原　義美</v>
               </pt>
               <pt idx="5">
-                <v>(担当CA不明)</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
@@ -3369,6 +3509,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -3436,7 +3584,7 @@
                 <v>中原　義美</v>
               </pt>
               <pt idx="5">
-                <v>(担当CA不明)</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
@@ -3459,7 +3607,7 @@
                 <v>0</v>
               </pt>
               <pt idx="5">
-                <v>0</v>
+                <v>2</v>
               </pt>
             </numLit>
           </val>
@@ -3505,7 +3653,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="4"/>
+          <max val="3"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -3523,6 +3671,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -3590,7 +3746,7 @@
                 <v>中原　義美</v>
               </pt>
               <pt idx="5">
-                <v>(担当CA不明)</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
@@ -3677,6 +3833,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -3727,7 +3891,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="13"/>
+              <ptCount val="9"/>
               <pt idx="0">
                 <v>加藤　英基</v>
               </pt>
@@ -3753,25 +3917,13 @@
                 <v>岩坪　公夫</v>
               </pt>
               <pt idx="8">
-                <v>落合　典彦</v>
-              </pt>
-              <pt idx="9">
-                <v>鈴木　聡</v>
-              </pt>
-              <pt idx="10">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="11">
-                <v>前野　正樹</v>
-              </pt>
-              <pt idx="12">
-                <v>石澤　直道</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="13"/>
+              <ptCount val="9"/>
               <pt idx="0">
                 <v>0</v>
               </pt>
@@ -3797,18 +3949,6 @@
                 <v>0</v>
               </pt>
               <pt idx="8">
-                <v>0</v>
-              </pt>
-              <pt idx="9">
-                <v>0</v>
-              </pt>
-              <pt idx="10">
-                <v>0</v>
-              </pt>
-              <pt idx="11">
-                <v>0</v>
-              </pt>
-              <pt idx="12">
                 <v>0</v>
               </pt>
             </numLit>
@@ -3873,6 +4013,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -3940,7 +4088,7 @@
                 <v>中原　義美</v>
               </pt>
               <pt idx="5">
-                <v>(担当CA不明)</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
@@ -4027,6 +4175,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -4088,7 +4244,7 @@
                 <v>樫原　純二</v>
               </pt>
               <pt idx="3">
-                <v>(担当CA不明)</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
@@ -4169,6 +4325,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -4230,7 +4394,7 @@
                 <v>樫原　純二</v>
               </pt>
               <pt idx="3">
-                <v>(担当CA不明)</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
@@ -4293,7 +4457,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="2"/>
+          <max val="1"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -4311,6 +4475,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -4372,7 +4544,7 @@
                 <v>樫原　純二</v>
               </pt>
               <pt idx="3">
-                <v>(担当CA不明)</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
@@ -4435,7 +4607,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="2"/>
+          <max val="1"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -4453,6 +4625,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -4514,7 +4694,7 @@
                 <v>樫原　純二</v>
               </pt>
               <pt idx="3">
-                <v>(担当CA不明)</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
@@ -4595,6 +4775,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -4656,7 +4844,7 @@
                 <v>樫原　純二</v>
               </pt>
               <pt idx="3">
-                <v>(担当CA不明)</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
@@ -4737,6 +4925,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -4798,7 +4994,7 @@
                 <v>樫原　純二</v>
               </pt>
               <pt idx="3">
-                <v>(担当CA不明)</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
@@ -4861,7 +5057,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="5"/>
+          <max val="4"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -4879,6 +5075,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -4940,7 +5144,7 @@
                 <v>樫原　純二</v>
               </pt>
               <pt idx="3">
-                <v>(担当CA不明)</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
@@ -5021,6 +5225,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -5082,7 +5294,7 @@
                 <v>樫原　純二</v>
               </pt>
               <pt idx="3">
-                <v>(担当CA不明)</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
@@ -5096,7 +5308,7 @@
                 <v>0</v>
               </pt>
               <pt idx="2">
-                <v>1</v>
+                <v>2</v>
               </pt>
               <pt idx="3">
                 <v>1</v>
@@ -5163,6 +5375,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -5224,7 +5444,7 @@
                 <v>樫原　純二</v>
               </pt>
               <pt idx="3">
-                <v>(担当CA不明)</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
@@ -5287,7 +5507,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="2"/>
+          <max val="1"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -5305,6 +5525,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -5355,7 +5583,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="13"/>
+              <ptCount val="9"/>
               <pt idx="0">
                 <v>加藤　英基</v>
               </pt>
@@ -5381,25 +5609,13 @@
                 <v>岩坪　公夫</v>
               </pt>
               <pt idx="8">
-                <v>落合　典彦</v>
-              </pt>
-              <pt idx="9">
-                <v>鈴木　聡</v>
-              </pt>
-              <pt idx="10">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="11">
-                <v>前野　正樹</v>
-              </pt>
-              <pt idx="12">
-                <v>石澤　直道</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="13"/>
+              <ptCount val="9"/>
               <pt idx="0">
                 <v>1</v>
               </pt>
@@ -5410,7 +5626,7 @@
                 <v>2</v>
               </pt>
               <pt idx="3">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="4">
                 <v>0</v>
@@ -5426,18 +5642,6 @@
               </pt>
               <pt idx="8">
                 <v>1</v>
-              </pt>
-              <pt idx="9">
-                <v>0</v>
-              </pt>
-              <pt idx="10">
-                <v>0</v>
-              </pt>
-              <pt idx="11">
-                <v>0</v>
-              </pt>
-              <pt idx="12">
-                <v>0</v>
               </pt>
             </numLit>
           </val>
@@ -5501,6 +5705,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -5562,7 +5774,7 @@
                 <v>樫原　純二</v>
               </pt>
               <pt idx="3">
-                <v>(担当CA不明)</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
@@ -5625,7 +5837,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="2"/>
+          <max val="1"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -5643,6 +5855,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -5693,22 +5913,28 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="2"/>
+              <ptCount val="3"/>
               <pt idx="0">
                 <v>大森　英樹</v>
               </pt>
               <pt idx="1">
                 <v>赤平　恵一</v>
+              </pt>
+              <pt idx="2">
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="2"/>
+              <ptCount val="3"/>
               <pt idx="0">
                 <v>0</v>
               </pt>
               <pt idx="1">
+                <v>0</v>
+              </pt>
+              <pt idx="2">
                 <v>0</v>
               </pt>
             </numLit>
@@ -5773,6 +5999,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -5823,22 +6057,28 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="2"/>
+              <ptCount val="3"/>
               <pt idx="0">
                 <v>大森　英樹</v>
               </pt>
               <pt idx="1">
                 <v>赤平　恵一</v>
+              </pt>
+              <pt idx="2">
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="2"/>
+              <ptCount val="3"/>
               <pt idx="0">
                 <v>0</v>
               </pt>
               <pt idx="1">
+                <v>0</v>
+              </pt>
+              <pt idx="2">
                 <v>0</v>
               </pt>
             </numLit>
@@ -5903,6 +6143,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -5953,22 +6201,28 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="2"/>
+              <ptCount val="3"/>
               <pt idx="0">
                 <v>大森　英樹</v>
               </pt>
               <pt idx="1">
                 <v>赤平　恵一</v>
+              </pt>
+              <pt idx="2">
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="2"/>
+              <ptCount val="3"/>
               <pt idx="0">
                 <v>0</v>
               </pt>
               <pt idx="1">
+                <v>0</v>
+              </pt>
+              <pt idx="2">
                 <v>0</v>
               </pt>
             </numLit>
@@ -6033,6 +6287,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -6083,23 +6345,29 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="2"/>
+              <ptCount val="3"/>
               <pt idx="0">
                 <v>大森　英樹</v>
               </pt>
               <pt idx="1">
                 <v>赤平　恵一</v>
+              </pt>
+              <pt idx="2">
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="2"/>
+              <ptCount val="3"/>
               <pt idx="0">
                 <v>5</v>
               </pt>
               <pt idx="1">
                 <v>2</v>
+              </pt>
+              <pt idx="2">
+                <v>0</v>
               </pt>
             </numLit>
           </val>
@@ -6163,6 +6431,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -6213,22 +6489,28 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="2"/>
+              <ptCount val="3"/>
               <pt idx="0">
                 <v>大森　英樹</v>
               </pt>
               <pt idx="1">
                 <v>赤平　恵一</v>
+              </pt>
+              <pt idx="2">
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="2"/>
+              <ptCount val="3"/>
               <pt idx="0">
                 <v>1</v>
               </pt>
               <pt idx="1">
+                <v>0</v>
+              </pt>
+              <pt idx="2">
                 <v>0</v>
               </pt>
             </numLit>
@@ -6275,7 +6557,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="4"/>
+          <max val="3"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -6293,6 +6575,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -6343,23 +6633,29 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="2"/>
+              <ptCount val="3"/>
               <pt idx="0">
                 <v>大森　英樹</v>
               </pt>
               <pt idx="1">
                 <v>赤平　恵一</v>
+              </pt>
+              <pt idx="2">
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="2"/>
+              <ptCount val="3"/>
               <pt idx="0">
                 <v>3</v>
               </pt>
               <pt idx="1">
                 <v>2</v>
+              </pt>
+              <pt idx="2">
+                <v>0</v>
               </pt>
             </numLit>
           </val>
@@ -6405,7 +6701,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="8"/>
+          <max val="5"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -6423,6 +6719,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -6473,23 +6777,29 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="2"/>
+              <ptCount val="3"/>
               <pt idx="0">
                 <v>大森　英樹</v>
               </pt>
               <pt idx="1">
                 <v>赤平　恵一</v>
+              </pt>
+              <pt idx="2">
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="2"/>
+              <ptCount val="3"/>
               <pt idx="0">
                 <v>2</v>
               </pt>
               <pt idx="1">
                 <v>4</v>
+              </pt>
+              <pt idx="2">
+                <v>0</v>
               </pt>
             </numLit>
           </val>
@@ -6553,6 +6863,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -6603,23 +6921,29 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="2"/>
+              <ptCount val="3"/>
               <pt idx="0">
                 <v>大森　英樹</v>
               </pt>
               <pt idx="1">
                 <v>赤平　恵一</v>
+              </pt>
+              <pt idx="2">
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="2"/>
+              <ptCount val="3"/>
               <pt idx="0">
-                <v>7</v>
+                <v>8</v>
               </pt>
               <pt idx="1">
                 <v>7</v>
+              </pt>
+              <pt idx="2">
+                <v>0</v>
               </pt>
             </numLit>
           </val>
@@ -6665,7 +6989,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="7"/>
+          <max val="8"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -6683,6 +7007,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -6733,22 +7065,28 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="2"/>
+              <ptCount val="3"/>
               <pt idx="0">
                 <v>大森　英樹</v>
               </pt>
               <pt idx="1">
                 <v>赤平　恵一</v>
+              </pt>
+              <pt idx="2">
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="2"/>
+              <ptCount val="3"/>
               <pt idx="0">
                 <v>0</v>
               </pt>
               <pt idx="1">
+                <v>0</v>
+              </pt>
+              <pt idx="2">
                 <v>0</v>
               </pt>
             </numLit>
@@ -6813,6 +7151,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -6863,7 +7209,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="13"/>
+              <ptCount val="9"/>
               <pt idx="0">
                 <v>加藤　英基</v>
               </pt>
@@ -6889,25 +7235,13 @@
                 <v>岩坪　公夫</v>
               </pt>
               <pt idx="8">
-                <v>落合　典彦</v>
-              </pt>
-              <pt idx="9">
-                <v>鈴木　聡</v>
-              </pt>
-              <pt idx="10">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="11">
-                <v>前野　正樹</v>
-              </pt>
-              <pt idx="12">
-                <v>石澤　直道</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="13"/>
+              <ptCount val="9"/>
               <pt idx="0">
                 <v>1</v>
               </pt>
@@ -6915,10 +7249,10 @@
                 <v>0</v>
               </pt>
               <pt idx="2">
-                <v>5</v>
+                <v>8</v>
               </pt>
               <pt idx="3">
-                <v>3</v>
+                <v>4</v>
               </pt>
               <pt idx="4">
                 <v>1</v>
@@ -6933,19 +7267,7 @@
                 <v>0</v>
               </pt>
               <pt idx="8">
-                <v>1</v>
-              </pt>
-              <pt idx="9">
-                <v>1</v>
-              </pt>
-              <pt idx="10">
-                <v>0</v>
-              </pt>
-              <pt idx="11">
-                <v>0</v>
-              </pt>
-              <pt idx="12">
-                <v>0</v>
+                <v>2</v>
               </pt>
             </numLit>
           </val>
@@ -6991,7 +7313,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="5"/>
+          <max val="8"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -7009,6 +7331,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -7059,22 +7389,28 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="2"/>
+              <ptCount val="3"/>
               <pt idx="0">
                 <v>大森　英樹</v>
               </pt>
               <pt idx="1">
                 <v>赤平　恵一</v>
+              </pt>
+              <pt idx="2">
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="2"/>
+              <ptCount val="3"/>
               <pt idx="0">
                 <v>0</v>
               </pt>
               <pt idx="1">
+                <v>0</v>
+              </pt>
+              <pt idx="2">
                 <v>0</v>
               </pt>
             </numLit>
@@ -7139,6 +7475,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -7197,7 +7541,7 @@
                 <v>今泉　健一</v>
               </pt>
               <pt idx="2">
-                <v>(担当CA不明)</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
@@ -7275,6 +7619,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -7333,7 +7685,7 @@
                 <v>今泉　健一</v>
               </pt>
               <pt idx="2">
-                <v>(担当CA不明)</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
@@ -7344,7 +7696,7 @@
                 <v>0</v>
               </pt>
               <pt idx="1">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="2">
                 <v>0</v>
@@ -7393,7 +7745,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="2"/>
+          <max val="1"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -7411,6 +7763,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -7469,7 +7829,7 @@
                 <v>今泉　健一</v>
               </pt>
               <pt idx="2">
-                <v>(担当CA不明)</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
@@ -7529,7 +7889,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="2"/>
+          <max val="1"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -7547,6 +7907,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -7605,7 +7973,7 @@
                 <v>今泉　健一</v>
               </pt>
               <pt idx="2">
-                <v>(担当CA不明)</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
@@ -7619,7 +7987,7 @@
                 <v>0</v>
               </pt>
               <pt idx="2">
-                <v>0</v>
+                <v>1</v>
               </pt>
             </numLit>
           </val>
@@ -7665,7 +8033,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="2"/>
+          <max val="1"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -7683,6 +8051,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -7741,7 +8117,7 @@
                 <v>今泉　健一</v>
               </pt>
               <pt idx="2">
-                <v>(担当CA不明)</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
@@ -7752,7 +8128,7 @@
                 <v>0</v>
               </pt>
               <pt idx="1">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="2">
                 <v>0</v>
@@ -7801,7 +8177,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="4"/>
+          <max val="3"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -7819,6 +8195,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -7877,7 +8261,7 @@
                 <v>今泉　健一</v>
               </pt>
               <pt idx="2">
-                <v>(担当CA不明)</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
@@ -7888,7 +8272,7 @@
                 <v>0</v>
               </pt>
               <pt idx="1">
-                <v>0</v>
+                <v>1</v>
               </pt>
               <pt idx="2">
                 <v>1</v>
@@ -7937,7 +8321,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="7"/>
+          <max val="5"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -7955,6 +8339,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -8013,7 +8405,7 @@
                 <v>今泉　健一</v>
               </pt>
               <pt idx="2">
-                <v>(担当CA不明)</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
@@ -8073,7 +8465,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="2"/>
+          <max val="1"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -8091,6 +8483,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -8149,7 +8549,7 @@
                 <v>今泉　健一</v>
               </pt>
               <pt idx="2">
-                <v>(担当CA不明)</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
@@ -8209,7 +8609,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="3"/>
+          <max val="2"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -8227,6 +8627,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -8285,7 +8693,7 @@
                 <v>今泉　健一</v>
               </pt>
               <pt idx="2">
-                <v>(担当CA不明)</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
@@ -8345,7 +8753,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="2"/>
+          <max val="1"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -8363,6 +8771,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -8413,7 +8829,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="13"/>
+              <ptCount val="9"/>
               <pt idx="0">
                 <v>加藤　英基</v>
               </pt>
@@ -8439,25 +8855,13 @@
                 <v>岩坪　公夫</v>
               </pt>
               <pt idx="8">
-                <v>落合　典彦</v>
-              </pt>
-              <pt idx="9">
-                <v>鈴木　聡</v>
-              </pt>
-              <pt idx="10">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="11">
-                <v>前野　正樹</v>
-              </pt>
-              <pt idx="12">
-                <v>石澤　直道</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="13"/>
+              <ptCount val="9"/>
               <pt idx="0">
                 <v>0</v>
               </pt>
@@ -8465,7 +8869,7 @@
                 <v>0</v>
               </pt>
               <pt idx="2">
-                <v>4</v>
+                <v>5</v>
               </pt>
               <pt idx="3">
                 <v>0</v>
@@ -8483,18 +8887,6 @@
                 <v>0</v>
               </pt>
               <pt idx="8">
-                <v>0</v>
-              </pt>
-              <pt idx="9">
-                <v>0</v>
-              </pt>
-              <pt idx="10">
-                <v>0</v>
-              </pt>
-              <pt idx="11">
-                <v>0</v>
-              </pt>
-              <pt idx="12">
                 <v>0</v>
               </pt>
             </numLit>
@@ -8541,7 +8933,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="8"/>
+          <max val="7"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -8559,6 +8951,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -8617,7 +9017,7 @@
                 <v>今泉　健一</v>
               </pt>
               <pt idx="2">
-                <v>(担当CA不明)</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
@@ -8677,7 +9077,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="2"/>
+          <max val="1"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -8695,6 +9095,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -8834,6 +9242,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -8973,6 +9389,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -9112,6 +9536,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -9251,6 +9683,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -9390,6 +9830,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -9529,6 +9977,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -9668,6 +10124,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -9807,6 +10271,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -9946,6 +10418,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -9996,7 +10476,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="13"/>
+              <ptCount val="9"/>
               <pt idx="0">
                 <v>加藤　英基</v>
               </pt>
@@ -10022,25 +10502,13 @@
                 <v>岩坪　公夫</v>
               </pt>
               <pt idx="8">
-                <v>落合　典彦</v>
-              </pt>
-              <pt idx="9">
-                <v>鈴木　聡</v>
-              </pt>
-              <pt idx="10">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="11">
-                <v>前野　正樹</v>
-              </pt>
-              <pt idx="12">
-                <v>石澤　直道</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="13"/>
+              <ptCount val="9"/>
               <pt idx="0">
                 <v>0</v>
               </pt>
@@ -10066,18 +10534,6 @@
                 <v>0</v>
               </pt>
               <pt idx="8">
-                <v>0</v>
-              </pt>
-              <pt idx="9">
-                <v>0</v>
-              </pt>
-              <pt idx="10">
-                <v>0</v>
-              </pt>
-              <pt idx="11">
-                <v>0</v>
-              </pt>
-              <pt idx="12">
                 <v>0</v>
               </pt>
             </numLit>
@@ -10142,6 +10598,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -10281,6 +10745,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -10331,7 +10803,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="13"/>
+              <ptCount val="9"/>
               <pt idx="0">
                 <v>加藤　英基</v>
               </pt>
@@ -10357,25 +10829,13 @@
                 <v>岩坪　公夫</v>
               </pt>
               <pt idx="8">
-                <v>落合　典彦</v>
-              </pt>
-              <pt idx="9">
-                <v>鈴木　聡</v>
-              </pt>
-              <pt idx="10">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="11">
-                <v>前野　正樹</v>
-              </pt>
-              <pt idx="12">
-                <v>石澤　直道</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="13"/>
+              <ptCount val="9"/>
               <pt idx="0">
                 <v>1</v>
               </pt>
@@ -10383,37 +10843,25 @@
                 <v>0</v>
               </pt>
               <pt idx="2">
+                <v>5</v>
+              </pt>
+              <pt idx="3">
                 <v>3</v>
               </pt>
-              <pt idx="3">
+              <pt idx="4">
+                <v>0</v>
+              </pt>
+              <pt idx="5">
+                <v>0</v>
+              </pt>
+              <pt idx="6">
                 <v>2</v>
               </pt>
-              <pt idx="4">
-                <v>0</v>
-              </pt>
-              <pt idx="5">
-                <v>0</v>
-              </pt>
-              <pt idx="6">
-                <v>1</v>
-              </pt>
               <pt idx="7">
                 <v>0</v>
               </pt>
               <pt idx="8">
-                <v>0</v>
-              </pt>
-              <pt idx="9">
-                <v>0</v>
-              </pt>
-              <pt idx="10">
-                <v>1</v>
-              </pt>
-              <pt idx="11">
-                <v>1</v>
-              </pt>
-              <pt idx="12">
-                <v>1</v>
+                <v>3</v>
               </pt>
             </numLit>
           </val>
@@ -10459,7 +10907,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="4"/>
+          <max val="5"/>
           <min val="0"/>
         </scaling>
         <delete val="0"/>
@@ -10477,6 +10925,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -10527,7 +10983,7 @@
           </spPr>
           <cat>
             <strLit>
-              <ptCount val="13"/>
+              <ptCount val="9"/>
               <pt idx="0">
                 <v>加藤　英基</v>
               </pt>
@@ -10553,25 +11009,13 @@
                 <v>岩坪　公夫</v>
               </pt>
               <pt idx="8">
-                <v>落合　典彦</v>
-              </pt>
-              <pt idx="9">
-                <v>鈴木　聡</v>
-              </pt>
-              <pt idx="10">
-                <v>(担当CA不明)</v>
-              </pt>
-              <pt idx="11">
-                <v>前野　正樹</v>
-              </pt>
-              <pt idx="12">
-                <v>石澤　直道</v>
+                <v>その他</v>
               </pt>
             </strLit>
           </cat>
           <val>
             <numLit>
-              <ptCount val="13"/>
+              <ptCount val="9"/>
               <pt idx="0">
                 <v>0</v>
               </pt>
@@ -10597,18 +11041,6 @@
                 <v>0</v>
               </pt>
               <pt idx="8">
-                <v>0</v>
-              </pt>
-              <pt idx="9">
-                <v>0</v>
-              </pt>
-              <pt idx="10">
-                <v>0</v>
-              </pt>
-              <pt idx="11">
-                <v>0</v>
-              </pt>
-              <pt idx="12">
                 <v>0</v>
               </pt>
             </numLit>
@@ -10673,6 +11105,14 @@
     <plotVisOnly val="1"/>
     <dispBlanksAs val="gap"/>
   </chart>
+  <spPr>
+    <a:ln w="9525">
+      <a:solidFill>
+        <a:srgbClr val="B0B0B0"/>
+      </a:solidFill>
+      <a:prstDash val="solid"/>
+    </a:ln>
+  </spPr>
 </chartSpace>
 </file>
 
@@ -10685,7 +11125,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -10707,7 +11147,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -10729,7 +11169,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="3" name="Chart 3"/>
@@ -10751,7 +11191,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="4" name="Chart 4"/>
@@ -10773,7 +11213,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="5" name="Chart 5"/>
@@ -10795,7 +11235,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="6" name="Chart 6"/>
@@ -10817,7 +11257,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="7" name="Chart 7"/>
@@ -10839,7 +11279,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="8" name="Chart 8"/>
@@ -10861,7 +11301,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="9" name="Chart 9"/>
@@ -10883,7 +11323,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="10" name="Chart 10"/>
@@ -10910,7 +11350,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -10932,7 +11372,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -10954,7 +11394,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="3" name="Chart 3"/>
@@ -10976,7 +11416,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="4" name="Chart 4"/>
@@ -10998,7 +11438,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="5" name="Chart 5"/>
@@ -11020,7 +11460,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="6" name="Chart 6"/>
@@ -11042,7 +11482,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="7" name="Chart 7"/>
@@ -11064,7 +11504,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="8" name="Chart 8"/>
@@ -11086,7 +11526,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="9" name="Chart 9"/>
@@ -11108,7 +11548,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="10" name="Chart 10"/>
@@ -11135,7 +11575,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -11157,7 +11597,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -11179,7 +11619,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="3" name="Chart 3"/>
@@ -11201,7 +11641,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="4" name="Chart 4"/>
@@ -11223,7 +11663,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="5" name="Chart 5"/>
@@ -11245,7 +11685,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="6" name="Chart 6"/>
@@ -11267,7 +11707,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="7" name="Chart 7"/>
@@ -11289,7 +11729,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="8" name="Chart 8"/>
@@ -11311,7 +11751,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="9" name="Chart 9"/>
@@ -11333,7 +11773,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="10" name="Chart 10"/>
@@ -11360,7 +11800,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -11382,7 +11822,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -11404,7 +11844,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="3" name="Chart 3"/>
@@ -11426,7 +11866,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="4" name="Chart 4"/>
@@ -11448,7 +11888,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="5" name="Chart 5"/>
@@ -11470,7 +11910,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="6" name="Chart 6"/>
@@ -11492,7 +11932,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="7" name="Chart 7"/>
@@ -11514,7 +11954,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="8" name="Chart 8"/>
@@ -11536,7 +11976,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="9" name="Chart 9"/>
@@ -11558,7 +11998,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="10" name="Chart 10"/>
@@ -11585,7 +12025,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -11607,7 +12047,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -11629,7 +12069,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="3" name="Chart 3"/>
@@ -11651,7 +12091,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="4" name="Chart 4"/>
@@ -11673,7 +12113,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="5" name="Chart 5"/>
@@ -11695,7 +12135,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="6" name="Chart 6"/>
@@ -11717,7 +12157,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="7" name="Chart 7"/>
@@ -11739,7 +12179,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="8" name="Chart 8"/>
@@ -11761,7 +12201,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="9" name="Chart 9"/>
@@ -11783,7 +12223,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="10" name="Chart 10"/>
@@ -11810,7 +12250,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -11832,7 +12272,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -11854,7 +12294,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="3" name="Chart 3"/>
@@ -11876,7 +12316,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="4" name="Chart 4"/>
@@ -11898,7 +12338,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="5" name="Chart 5"/>
@@ -11920,7 +12360,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="6" name="Chart 6"/>
@@ -11942,7 +12382,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="7" name="Chart 7"/>
@@ -11964,7 +12404,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="8" name="Chart 8"/>
@@ -11986,7 +12426,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="9" name="Chart 9"/>
@@ -12008,7 +12448,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="10" name="Chart 10"/>
@@ -12035,7 +12475,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -12057,7 +12497,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
@@ -12079,7 +12519,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="3" name="Chart 3"/>
@@ -12101,7 +12541,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="4" name="Chart 4"/>
@@ -12123,7 +12563,7 @@
       <row>2</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="5" name="Chart 5"/>
@@ -12145,7 +12585,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="6" name="Chart 6"/>
@@ -12167,7 +12607,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="7" name="Chart 7"/>
@@ -12189,7 +12629,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="8" name="Chart 8"/>
@@ -12211,7 +12651,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="9" name="Chart 9"/>
@@ -12233,7 +12673,7 @@
       <row>4</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="2880000" cy="5040000"/>
+    <ext cx="2880000" cy="4500000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="10" name="Chart 10"/>
@@ -12540,7 +12980,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:U13"/>
+  <dimension ref="A1:Q13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42.48" customWidth="1" min="1" max="1"/>
@@ -12558,10 +12998,6 @@
     <col width="9" customWidth="1" min="15" max="15"/>
     <col width="9" customWidth="1" min="16" max="16"/>
     <col width="9" customWidth="1" min="17" max="17"/>
-    <col width="9" customWidth="1" min="18" max="18"/>
-    <col width="9" customWidth="1" min="19" max="19"/>
-    <col width="9" customWidth="1" min="20" max="20"/>
-    <col width="9" customWidth="1" min="21" max="21"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -12572,7 +13008,7 @@
       </c>
     </row>
     <row r="2" ht="8" customHeight="1"/>
-    <row r="3" ht="396.8503937007874" customHeight="1">
+    <row r="3" ht="358.5826771653543" customHeight="1">
       <c r="H3" s="2" t="inlineStr">
         <is>
           <t>商品名</t>
@@ -12643,49 +13079,13 @@
       </c>
       <c r="Q3" s="3" t="inlineStr">
         <is>
-          <t>落
-合
-典
-彦</t>
+          <t>そ
+の
+他</t>
         </is>
       </c>
-      <c r="R3" s="3" t="inlineStr">
-        <is>
-          <t>鈴
-木
-聡</t>
-        </is>
-      </c>
-      <c r="S3" s="3" t="inlineStr">
-        <is>
-          <t>(
-担
-当
-C
-A
-不
-明
-)</t>
-        </is>
-      </c>
-      <c r="T3" s="3" t="inlineStr">
-        <is>
-          <t>前
-野
-正
-樹</t>
-        </is>
-      </c>
-      <c r="U3" s="3" t="inlineStr">
-        <is>
-          <t>石
-澤
-直
-道</t>
-        </is>
-      </c>
     </row>
-    <row r="4" ht="51.02362204724409" customHeight="1">
+    <row r="4" ht="42.51968503937007" customHeight="1">
       <c r="H4" s="4" t="inlineStr">
         <is>
           <t>エンジンリフレッシュ</t>
@@ -12718,20 +13118,8 @@
       <c r="Q4" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="R4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" s="4" t="n">
-        <v>0</v>
-      </c>
     </row>
-    <row r="5" ht="396.8503937007874" customHeight="1">
+    <row r="5" ht="358.5826771653543" customHeight="1">
       <c r="H5" s="4" t="inlineStr">
         <is>
           <t>エアコン潤滑剤 NC200マキシクール</t>
@@ -12764,20 +13152,8 @@
       <c r="Q5" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="R5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" s="4" t="n">
-        <v>0</v>
-      </c>
     </row>
-    <row r="6">
+    <row r="6" ht="15" customHeight="1">
       <c r="H6" s="4" t="inlineStr">
         <is>
           <t>ウィンドウ撥水12カ月</t>
@@ -12810,20 +13186,8 @@
       <c r="Q6" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="R6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" s="4" t="n">
-        <v>0</v>
-      </c>
     </row>
-    <row r="7">
+    <row r="7" ht="15" customHeight="1">
       <c r="H7" s="4" t="inlineStr">
         <is>
           <t>エアコン/ヒーター洗浄12カ月</t>
@@ -12839,7 +13203,7 @@
         <v>2</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" s="4" t="n">
         <v>0</v>
@@ -12856,20 +13220,8 @@
       <c r="Q7" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="R7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U7" s="4" t="n">
-        <v>0</v>
-      </c>
     </row>
-    <row r="8">
+    <row r="8" ht="15" customHeight="1">
       <c r="H8" s="4" t="inlineStr">
         <is>
           <t>メタルトリートメント MT-10</t>
@@ -12882,10 +13234,10 @@
         <v>0</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M8" s="4" t="n">
         <v>1</v>
@@ -12900,19 +13252,7 @@
         <v>0</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="R8" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="S8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U8" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -12928,7 +13268,7 @@
         <v>0</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L9" s="4" t="n">
         <v>0</v>
@@ -12946,18 +13286,6 @@
         <v>0</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -12994,18 +13322,6 @@
       <c r="Q10" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="R10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" s="4" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="11">
       <c r="H11" s="4" t="inlineStr">
@@ -13020,37 +13336,25 @@
         <v>0</v>
       </c>
       <c r="K11" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="L11" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="L11" s="4" t="n">
+      <c r="M11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="M11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="P11" s="4" t="n">
         <v>0</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="T11" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="U11" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -13086,18 +13390,6 @@
       <c r="Q12" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="R12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U12" s="4" t="n">
-        <v>0</v>
-      </c>
     </row>
     <row r="13">
       <c r="H13" s="4" t="inlineStr">
@@ -13112,7 +13404,7 @@
         <v>0</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" s="4" t="n">
         <v>0</v>
@@ -13130,22 +13422,11 @@
         <v>0</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" s="4" t="n">
         <v>0</v>
       </c>
     </row>
   </sheetData>
+  <printOptions horizontalCentered="0" verticalCentered="1"/>
   <pageMargins left="0.2" right="0.2" top="0.2" bottom="0.2" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="1" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -13158,7 +13439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:O13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42.48" customWidth="1" min="1" max="1"/>
@@ -13173,6 +13454,7 @@
     <col width="9" customWidth="1" min="12" max="12"/>
     <col width="9" customWidth="1" min="13" max="13"/>
     <col width="9" customWidth="1" min="14" max="14"/>
+    <col width="9" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -13183,7 +13465,7 @@
       </c>
     </row>
     <row r="2" ht="8" customHeight="1"/>
-    <row r="3" ht="396.8503937007874" customHeight="1">
+    <row r="3" ht="358.5826771653543" customHeight="1">
       <c r="H3" s="2" t="inlineStr">
         <is>
           <t>商品名</t>
@@ -13235,8 +13517,15 @@
 久</t>
         </is>
       </c>
+      <c r="O3" s="3" t="inlineStr">
+        <is>
+          <t>そ
+の
+他</t>
+        </is>
+      </c>
     </row>
-    <row r="4" ht="51.02362204724409" customHeight="1">
+    <row r="4" ht="42.51968503937007" customHeight="1">
       <c r="H4" s="4" t="inlineStr">
         <is>
           <t>エンジンリフレッシュ</t>
@@ -13246,7 +13535,7 @@
         <v>0</v>
       </c>
       <c r="J4" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K4" s="4" t="n">
         <v>0</v>
@@ -13260,8 +13549,11 @@
       <c r="N4" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="O4" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
-    <row r="5" ht="396.8503937007874" customHeight="1">
+    <row r="5" ht="358.5826771653543" customHeight="1">
       <c r="H5" s="4" t="inlineStr">
         <is>
           <t>エアコン潤滑剤 NC200マキシクール</t>
@@ -13285,8 +13577,11 @@
       <c r="N5" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="O5" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
-    <row r="6">
+    <row r="6" ht="15" customHeight="1">
       <c r="H6" s="4" t="inlineStr">
         <is>
           <t>ウィンドウ撥水12カ月</t>
@@ -13310,8 +13605,11 @@
       <c r="N6" s="4" t="n">
         <v>1</v>
       </c>
+      <c r="O6" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
-    <row r="7">
+    <row r="7" ht="15" customHeight="1">
       <c r="H7" s="4" t="inlineStr">
         <is>
           <t>エアコン/ヒーター洗浄12カ月</t>
@@ -13327,7 +13625,7 @@
         <v>0</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" s="4" t="n">
         <v>1</v>
@@ -13335,8 +13633,11 @@
       <c r="N7" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="O7" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
-    <row r="8">
+    <row r="8" ht="15" customHeight="1">
       <c r="H8" s="4" t="inlineStr">
         <is>
           <t>メタルトリートメント MT-10</t>
@@ -13358,6 +13659,9 @@
         <v>0</v>
       </c>
       <c r="N8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -13385,6 +13689,9 @@
       <c r="N9" s="4" t="n">
         <v>1</v>
       </c>
+      <c r="O9" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="H10" s="4" t="inlineStr">
@@ -13410,6 +13717,9 @@
       <c r="N10" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="O10" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="H11" s="4" t="inlineStr">
@@ -13421,7 +13731,7 @@
         <v>0</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K11" s="4" t="n">
         <v>4</v>
@@ -13434,6 +13744,9 @@
       </c>
       <c r="N11" s="4" t="n">
         <v>2</v>
+      </c>
+      <c r="O11" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -13460,6 +13773,9 @@
       <c r="N12" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="O12" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="H13" s="4" t="inlineStr">
@@ -13485,8 +13801,12 @@
       <c r="N13" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="O13" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
+  <printOptions horizontalCentered="0" verticalCentered="1"/>
   <pageMargins left="0.2" right="0.2" top="0.2" bottom="0.2" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="1" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -13524,7 +13844,7 @@
       </c>
     </row>
     <row r="2" ht="8" customHeight="1"/>
-    <row r="3" ht="396.8503937007874" customHeight="1">
+    <row r="3" ht="358.5826771653543" customHeight="1">
       <c r="H3" s="2" t="inlineStr">
         <is>
           <t>商品名</t>
@@ -13571,31 +13891,26 @@
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>(
-担
-当
-C
-A
-不
-明
-)</t>
+          <t>そ
+の
+他</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="51.02362204724409" customHeight="1">
+    <row r="4" ht="42.51968503937007" customHeight="1">
       <c r="H4" s="4" t="inlineStr">
         <is>
           <t>エンジンリフレッシュ</t>
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>1</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" s="4" t="n">
         <v>0</v>
@@ -13607,14 +13922,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" ht="396.8503937007874" customHeight="1">
+    <row r="5" ht="358.5826771653543" customHeight="1">
       <c r="H5" s="4" t="inlineStr">
         <is>
           <t>エアコン潤滑剤 NC200マキシクール</t>
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>1</v>
@@ -13632,7 +13947,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="15" customHeight="1">
       <c r="H6" s="4" t="inlineStr">
         <is>
           <t>ウィンドウ撥水12カ月</t>
@@ -13657,14 +13972,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="15" customHeight="1">
       <c r="H7" s="4" t="inlineStr">
         <is>
           <t>エアコン/ヒーター洗浄12カ月</t>
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>1</v>
@@ -13682,14 +13997,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="15" customHeight="1">
       <c r="H8" s="4" t="inlineStr">
         <is>
           <t>メタルトリートメント MT-10</t>
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>1</v>
@@ -13714,7 +14029,7 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>1</v>
@@ -13779,7 +14094,7 @@
         <v>0</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -13833,6 +14148,7 @@
       </c>
     </row>
   </sheetData>
+  <printOptions horizontalCentered="0" verticalCentered="1"/>
   <pageMargins left="0.2" right="0.2" top="0.2" bottom="0.2" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="1" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -13868,7 +14184,7 @@
       </c>
     </row>
     <row r="2" ht="8" customHeight="1"/>
-    <row r="3" ht="396.8503937007874" customHeight="1">
+    <row r="3" ht="358.5826771653543" customHeight="1">
       <c r="H3" s="2" t="inlineStr">
         <is>
           <t>商品名</t>
@@ -13901,18 +14217,13 @@
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>(
-担
-当
-C
-A
-不
-明
-)</t>
+          <t>そ
+の
+他</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="51.02362204724409" customHeight="1">
+    <row r="4" ht="42.51968503937007" customHeight="1">
       <c r="H4" s="4" t="inlineStr">
         <is>
           <t>エンジンリフレッシュ</t>
@@ -13931,7 +14242,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" ht="396.8503937007874" customHeight="1">
+    <row r="5" ht="358.5826771653543" customHeight="1">
       <c r="H5" s="4" t="inlineStr">
         <is>
           <t>エアコン潤滑剤 NC200マキシクール</t>
@@ -13950,7 +14261,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="15" customHeight="1">
       <c r="H6" s="4" t="inlineStr">
         <is>
           <t>ウィンドウ撥水12カ月</t>
@@ -13969,7 +14280,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="15" customHeight="1">
       <c r="H7" s="4" t="inlineStr">
         <is>
           <t>エアコン/ヒーター洗浄12カ月</t>
@@ -13988,7 +14299,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="15" customHeight="1">
       <c r="H8" s="4" t="inlineStr">
         <is>
           <t>メタルトリートメント MT-10</t>
@@ -14058,7 +14369,7 @@
         <v>0</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L11" s="4" t="n">
         <v>1</v>
@@ -14103,6 +14414,7 @@
       </c>
     </row>
   </sheetData>
+  <printOptions horizontalCentered="0" verticalCentered="1"/>
   <pageMargins left="0.2" right="0.2" top="0.2" bottom="0.2" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="1" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -14115,7 +14427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42.48" customWidth="1" min="1" max="1"/>
@@ -14126,6 +14438,7 @@
     <col width="24" customWidth="1" min="8" max="8"/>
     <col width="9" customWidth="1" min="9" max="9"/>
     <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -14136,7 +14449,7 @@
       </c>
     </row>
     <row r="2" ht="8" customHeight="1"/>
-    <row r="3" ht="396.8503937007874" customHeight="1">
+    <row r="3" ht="358.5826771653543" customHeight="1">
       <c r="H3" s="2" t="inlineStr">
         <is>
           <t>商品名</t>
@@ -14158,8 +14471,15 @@
 一</t>
         </is>
       </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>そ
+の
+他</t>
+        </is>
+      </c>
     </row>
-    <row r="4" ht="51.02362204724409" customHeight="1">
+    <row r="4" ht="42.51968503937007" customHeight="1">
       <c r="H4" s="4" t="inlineStr">
         <is>
           <t>エンジンリフレッシュ</t>
@@ -14171,8 +14491,11 @@
       <c r="J4" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="K4" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
-    <row r="5" ht="396.8503937007874" customHeight="1">
+    <row r="5" ht="358.5826771653543" customHeight="1">
       <c r="H5" s="4" t="inlineStr">
         <is>
           <t>エアコン潤滑剤 NC200マキシクール</t>
@@ -14184,8 +14507,11 @@
       <c r="J5" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="K5" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
-    <row r="6">
+    <row r="6" ht="15" customHeight="1">
       <c r="H6" s="4" t="inlineStr">
         <is>
           <t>ウィンドウ撥水12カ月</t>
@@ -14197,8 +14523,11 @@
       <c r="J6" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="K6" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
-    <row r="7">
+    <row r="7" ht="15" customHeight="1">
       <c r="H7" s="4" t="inlineStr">
         <is>
           <t>エアコン/ヒーター洗浄12カ月</t>
@@ -14210,8 +14539,11 @@
       <c r="J7" s="4" t="n">
         <v>2</v>
       </c>
+      <c r="K7" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
-    <row r="8">
+    <row r="8" ht="15" customHeight="1">
       <c r="H8" s="4" t="inlineStr">
         <is>
           <t>メタルトリートメント MT-10</t>
@@ -14221,6 +14553,9 @@
         <v>1</v>
       </c>
       <c r="J8" s="4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -14236,6 +14571,9 @@
       <c r="J9" s="4" t="n">
         <v>2</v>
       </c>
+      <c r="K9" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="H10" s="4" t="inlineStr">
@@ -14249,6 +14587,9 @@
       <c r="J10" s="4" t="n">
         <v>4</v>
       </c>
+      <c r="K10" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="H11" s="4" t="inlineStr">
@@ -14257,10 +14598,13 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>7</v>
+      </c>
+      <c r="K11" s="4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -14275,6 +14619,9 @@
       <c r="J12" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="K12" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="H13" s="4" t="inlineStr">
@@ -14288,8 +14635,12 @@
       <c r="J13" s="4" t="n">
         <v>0</v>
       </c>
+      <c r="K13" s="4" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
+  <printOptions horizontalCentered="0" verticalCentered="1"/>
   <pageMargins left="0.2" right="0.2" top="0.2" bottom="0.2" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="1" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -14324,7 +14675,7 @@
       </c>
     </row>
     <row r="2" ht="8" customHeight="1"/>
-    <row r="3" ht="396.8503937007874" customHeight="1">
+    <row r="3" ht="358.5826771653543" customHeight="1">
       <c r="H3" s="2" t="inlineStr">
         <is>
           <t>商品名</t>
@@ -14348,18 +14699,13 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>(
-担
-当
-C
-A
-不
-明
-)</t>
+          <t>そ
+の
+他</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="51.02362204724409" customHeight="1">
+    <row r="4" ht="42.51968503937007" customHeight="1">
       <c r="H4" s="4" t="inlineStr">
         <is>
           <t>エンジンリフレッシュ</t>
@@ -14375,7 +14721,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" ht="396.8503937007874" customHeight="1">
+    <row r="5" ht="358.5826771653543" customHeight="1">
       <c r="H5" s="4" t="inlineStr">
         <is>
           <t>エアコン潤滑剤 NC200マキシクール</t>
@@ -14385,13 +14731,13 @@
         <v>0</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5" s="4" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="15" customHeight="1">
       <c r="H6" s="4" t="inlineStr">
         <is>
           <t>ウィンドウ撥水12カ月</t>
@@ -14407,7 +14753,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="15" customHeight="1">
       <c r="H7" s="4" t="inlineStr">
         <is>
           <t>エアコン/ヒーター洗浄12カ月</t>
@@ -14420,10 +14766,10 @@
         <v>0</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="15" customHeight="1">
       <c r="H8" s="4" t="inlineStr">
         <is>
           <t>メタルトリートメント MT-10</t>
@@ -14433,7 +14779,7 @@
         <v>0</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" s="4" t="n">
         <v>0</v>
@@ -14449,7 +14795,7 @@
         <v>0</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K9" s="4" t="n">
         <v>1</v>
@@ -14520,6 +14866,7 @@
       </c>
     </row>
   </sheetData>
+  <printOptions horizontalCentered="0" verticalCentered="1"/>
   <pageMargins left="0.2" right="0.2" top="0.2" bottom="0.2" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="1" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -14556,7 +14903,7 @@
       </c>
     </row>
     <row r="2" ht="8" customHeight="1"/>
-    <row r="3" ht="396.8503937007874" customHeight="1">
+    <row r="3" ht="358.5826771653543" customHeight="1">
       <c r="H3" s="2" t="inlineStr">
         <is>
           <t>商品名</t>
@@ -14602,7 +14949,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="51.02362204724409" customHeight="1">
+    <row r="4" ht="42.51968503937007" customHeight="1">
       <c r="H4" s="4" t="inlineStr">
         <is>
           <t>エンジンリフレッシュ</t>
@@ -14624,7 +14971,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" ht="396.8503937007874" customHeight="1">
+    <row r="5" ht="358.5826771653543" customHeight="1">
       <c r="H5" s="4" t="inlineStr">
         <is>
           <t>エアコン潤滑剤 NC200マキシクール</t>
@@ -14646,7 +14993,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" ht="15" customHeight="1">
       <c r="H6" s="4" t="inlineStr">
         <is>
           <t>ウィンドウ撥水12カ月</t>
@@ -14668,7 +15015,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="15" customHeight="1">
       <c r="H7" s="4" t="inlineStr">
         <is>
           <t>エアコン/ヒーター洗浄12カ月</t>
@@ -14690,7 +15037,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="15" customHeight="1">
       <c r="H8" s="4" t="inlineStr">
         <is>
           <t>メタルトリートメント MT-10</t>
@@ -14823,6 +15170,7 @@
       </c>
     </row>
   </sheetData>
+  <printOptions horizontalCentered="0" verticalCentered="1"/>
   <pageMargins left="0.2" right="0.2" top="0.2" bottom="0.2" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="1" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
